--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120836998</v>
       </c>
       <c r="B2" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>120836840</v>
       </c>
       <c r="B3" t="n">
-        <v>79216</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,244 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122649198</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långåsarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563369</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6516168</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>flyktläte</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122649199</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57536</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långåsarna, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>563332</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6516157</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>två som satt/ flög omkring och lät</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R4" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R5" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R4" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,34 +1012,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R5" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R4" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R5" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R4" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,34 +1012,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R5" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R4" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R5" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R4" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,34 +1012,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R5" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 46648-2024 artfynd.xlsx
+++ b/artfynd/A 46648-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122649198</v>
+        <v>122649199</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563369</v>
+        <v>563332</v>
       </c>
       <c r="R4" t="n">
-        <v>6516168</v>
+        <v>6516157</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>flyktläte</t>
+          <t>två som satt/ flög omkring och lät</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122649199</v>
+        <v>122649198</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långåsarna, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563332</v>
+        <v>563369</v>
       </c>
       <c r="R5" t="n">
-        <v>6516157</v>
+        <v>6516168</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>två som satt/ flög omkring och lät</t>
+          <t>flyktläte</t>
         </is>
       </c>
       <c r="AD5" t="b">
